--- a/crates/core/tests/fixtures/m2/Statistical.xlsx
+++ b/crates/core/tests/fixtures/m2/Statistical.xlsx
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="751">
   <si>
     <t>Description</t>
   </si>
@@ -239,6 +239,42 @@
     <t>=AVERAGEIF({1,2,3,4,5},"&lt;"&amp;3)</t>
   </si>
   <si>
+    <t>exact number match</t>
+  </si>
+  <si>
+    <t>=AVERAGEIF({10,20,30},20)</t>
+  </si>
+  <si>
+    <t>not-equal &lt;&gt; criterion -&gt; avg 1,3 = 2</t>
+  </si>
+  <si>
+    <t>=AVERAGEIF({1,2,3},"&lt;&gt;"&amp;2)</t>
+  </si>
+  <si>
+    <t>? wildcard single char: a? matches ab ac</t>
+  </si>
+  <si>
+    <t>=AVERAGEIF({"ab","ac","ba"},"a?",{10,20,30})</t>
+  </si>
+  <si>
+    <t>case-insensitive text match</t>
+  </si>
+  <si>
+    <t>=AVERAGEIF({"Apple","APPLE","banana"},"apple",{10,20,30})</t>
+  </si>
+  <si>
+    <t>&gt;= criterion</t>
+  </si>
+  <si>
+    <t>=AVERAGEIF({1,2,3,4,5},"&gt;="&amp;3)</t>
+  </si>
+  <si>
+    <t>coercion: criterion as number string</t>
+  </si>
+  <si>
+    <t>=AVERAGEIF({1,2,3},"2",{10,20,30})</t>
+  </si>
+  <si>
     <t>no match -&gt; #DIV/0!</t>
   </si>
   <si>
@@ -251,10 +287,10 @@
     <t>=ROUND(AVERAGEIF({1,2,3,4,5},"&gt;"&amp;2),4)</t>
   </si>
   <si>
-    <t>exact number match</t>
-  </si>
-  <si>
-    <t>=AVERAGEIF({10,20,30},20)</t>
+    <t>nested: AVERAGEIF vs AVERAGE same values</t>
+  </si>
+  <si>
+    <t>=ROUND(AVERAGEIF({1,2,3},"&gt;"&amp;0)-AVERAGE({1,2,3}),10)</t>
   </si>
   <si>
     <t>=AVERAGEIF()</t>
@@ -2980,10 +3016,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">ROUND(KURT({3,4,5,2,3,4,5,6,4,7}),4)</f>
@@ -2995,10 +3031,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">ROUND(KURT({1,2,3,4,5}),4)</f>
@@ -3010,10 +3046,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C4" s="4">
         <f>ROUND(KURT(2,2,2,3,3,3,4,4,4),4)</f>
@@ -3025,10 +3061,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C5" s="4">
         <f>ROUND(KURT(1,2,3,4,5,6,7),4)</f>
@@ -3040,10 +3076,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C6" s="4" t="str">
         <f>KURT(5,5,5,5,5)</f>
@@ -3055,10 +3091,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C7" s="4">
         <f>ROUND(KURT(1,2,3,4,5,6,7,8),4)</f>
@@ -3070,10 +3106,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="C8" s="7" t="b">
         <f t="array" ref="C8">ISNUMBER(KURT({1,2,3,4,5,6}))</f>
@@ -3085,10 +3121,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C9" s="10" t="str">
         <f>KURT(1,2,3)</f>
@@ -3103,7 +3139,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>KURT()</f>
@@ -3147,10 +3183,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">LARGE({3,1,4,1,5,9,2,6},1)</f>
@@ -3162,10 +3198,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">LARGE({3,1,4,1,5,9,2,6},2)</f>
@@ -3177,10 +3213,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">LARGE({3,1,4,1,5,9,2,6},3)</f>
@@ -3192,10 +3228,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">LARGE({1,2,3},3)</f>
@@ -3207,10 +3243,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">LARGE({5,5,5},1)</f>
@@ -3222,10 +3258,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">LARGE({5,5,5},2)</f>
@@ -3237,10 +3273,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C8" s="4">
         <f t="array" ref="C8">LARGE(42,1)</f>
@@ -3252,10 +3288,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">LARGE({1,2,3,4,5},1)+SMALL({1,2,3,4,5},1)</f>
@@ -3267,10 +3303,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">LARGE({1,2,3},0)</f>
@@ -3282,10 +3318,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C11" s="10" t="str">
         <f t="array" ref="C11">LARGE({1,2,3},4)</f>
@@ -3300,7 +3336,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C12" s="10" t="str">
         <f>LARGE()</f>
@@ -3344,10 +3380,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C2" s="4">
         <f>MAXA(1,2,3)</f>
@@ -3359,10 +3395,10 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="C3" s="13">
         <f>MAXA(TRUE,2,3)</f>
@@ -3374,10 +3410,10 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C4" s="13">
         <f>MAXA(FALSE,0)</f>
@@ -3389,10 +3425,10 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="C5" s="13" t="str">
         <f>MAXA("text",5)</f>
@@ -3407,7 +3443,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C6" s="4">
         <f>MAXA(-5,-3,-1)</f>
@@ -3419,10 +3455,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C7" s="4">
         <f>MAXA(-1,0,1)</f>
@@ -3434,10 +3470,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="C8" s="4">
         <f>MAXA(7)</f>
@@ -3449,10 +3485,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C9" s="4">
         <f>MAXA(3,3,3)</f>
@@ -3464,10 +3500,10 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C10" s="7">
         <f>MAXA(1,2,3)-MAX(1,2,3)</f>
@@ -3482,7 +3518,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>MAXA()</f>
@@ -3526,10 +3562,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="C2" s="4" t="str">
         <f t="array" ref="C2">MAXIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;"&amp;2)</f>
@@ -3541,10 +3577,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C3" s="4" t="str">
         <f t="array" ref="C3">MAXIFS({10,20,30},{"a","b","a"},"a")</f>
@@ -3556,10 +3592,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C4" s="4" t="str">
         <f t="array" ref="C4">MAXIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;"&amp;10)</f>
@@ -3574,7 +3610,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C5" s="4" t="str">
         <f t="array" ref="C5">MAXIFS({10,20,30},{1,2,3},2)</f>
@@ -3586,10 +3622,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C6" s="4" t="str">
         <f t="array" ref="C6">MAXIFS({1,2,3,4,5},{1,2,3,4,5},"&lt;"&amp;3)</f>
@@ -3601,10 +3637,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C7" s="4" t="str">
         <f t="array" ref="C7">MAXIFS({10,20,30},{1,2,3},"&gt;"&amp;0)</f>
@@ -3616,10 +3652,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C8" s="4" t="str">
         <f t="array" ref="C8">MAXIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;"&amp;1,{1,2,3,4,5},"&lt;"&amp;5)</f>
@@ -3631,10 +3667,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C9" s="7" t="str">
         <f t="array" ref="C9">MAX(MAXIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;"&amp;2),0)</f>
@@ -3649,7 +3685,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>MAXIFS()</f>
@@ -3693,10 +3729,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C2" s="4">
         <f>MEDIAN(1,2,3,4,5)</f>
@@ -3708,10 +3744,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C3" s="4">
         <f>MEDIAN(1,2,3,4)</f>
@@ -3723,10 +3759,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">MEDIAN({1,3,5,7,9})</f>
@@ -3738,10 +3774,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C5" s="4">
         <f>MEDIAN(5)</f>
@@ -3753,10 +3789,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C6" s="4">
         <f>MEDIAN(1,1,1)</f>
@@ -3771,7 +3807,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C7" s="4">
         <f>MEDIAN(3,7)</f>
@@ -3783,10 +3819,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C8" s="4">
         <f>MEDIAN(-3,-1,0,1,3)</f>
@@ -3798,10 +3834,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C9" s="4">
         <f>MEDIAN(5,1,3,4,2)</f>
@@ -3813,10 +3849,10 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C10" s="7">
         <f t="array" ref="C10">MEDIAN({1,2,3,4,5})-3</f>
@@ -3831,7 +3867,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>MEDIAN()</f>
@@ -3875,10 +3911,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C2" s="4">
         <f>MINA(1,2,3)</f>
@@ -3890,10 +3926,10 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C3" s="13">
         <f>MINA(TRUE,2,3)</f>
@@ -3905,10 +3941,10 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C4" s="13" t="str">
         <f>MINA("text",5)</f>
@@ -3920,10 +3956,10 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C5" s="13">
         <f>MINA(FALSE,1)</f>
@@ -3938,7 +3974,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C6" s="4">
         <f>MINA(-5,-3,-1)</f>
@@ -3950,10 +3986,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C7" s="4">
         <f>MINA(-1,0,1)</f>
@@ -3965,10 +4001,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C8" s="4">
         <f>MINA(7)</f>
@@ -3980,10 +4016,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C9" s="4">
         <f>MINA(3,3,3)</f>
@@ -3995,10 +4031,10 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C10" s="7">
         <f>MINA(1,2,3)-MIN(1,2,3)</f>
@@ -4013,7 +4049,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>MINA()</f>
@@ -4057,10 +4093,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C2" s="4" t="str">
         <f t="array" ref="C2">MINIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;"&amp;2)</f>
@@ -4072,10 +4108,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C3" s="4" t="str">
         <f t="array" ref="C3">MINIFS({10,20,30},{"a","b","a"},"a")</f>
@@ -4087,10 +4123,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C4" s="4" t="str">
         <f t="array" ref="C4">MINIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;"&amp;10)</f>
@@ -4105,7 +4141,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C5" s="4" t="str">
         <f t="array" ref="C5">MINIFS({10,20,30},{1,2,3},2)</f>
@@ -4117,10 +4153,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C6" s="4" t="str">
         <f t="array" ref="C6">MINIFS({1,2,3,4,5},{1,2,3,4,5},"&lt;"&amp;3)</f>
@@ -4132,10 +4168,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C7" s="4" t="str">
         <f t="array" ref="C7">MINIFS({10,20,30},{1,2,3},"&gt;"&amp;0)</f>
@@ -4147,10 +4183,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C8" s="4" t="str">
         <f t="array" ref="C8">MINIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;"&amp;1,{1,2,3,4,5},"&lt;"&amp;5)</f>
@@ -4162,10 +4198,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C9" s="7" t="str">
         <f t="array" ref="C9">MIN(MINIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;"&amp;2),10)</f>
@@ -4180,7 +4216,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>MINIFS()</f>
@@ -4224,10 +4260,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C2" s="4">
         <f>MODE(1,2,2,3)</f>
@@ -4239,10 +4275,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">MODE({1,1,2,3,3,3})</f>
@@ -4254,10 +4290,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="C4" s="4">
         <f>MODE(5,5,5)</f>
@@ -4269,10 +4305,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C5" s="4">
         <f>MODE(1,1,2,2)</f>
@@ -4284,10 +4320,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C6" s="4">
         <f>MODE(1,2,3,2,1,2,3,2)</f>
@@ -4299,10 +4335,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C7" s="4">
         <f>MODE(7,7)</f>
@@ -4314,10 +4350,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C8" s="7" t="b">
         <f>IF(MODE(1,2,2,3)=2,TRUE,FALSE)</f>
@@ -4329,10 +4365,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C9" s="10" t="str">
         <f>MODE(1,2,3)</f>
@@ -4347,7 +4383,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>MODE()</f>
@@ -4391,10 +4427,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">_xlfn.MODE.MULT({1,2,2,3})</f>
@@ -4406,10 +4442,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C3" s="4" t="b">
         <f t="array" ref="C3">ISNUMBER(_xlfn.MODE.MULT({1,1,2,2,3}))</f>
@@ -4421,10 +4457,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">SUM(_xlfn.MODE.MULT({1,1,2,2,3}))</f>
@@ -4436,10 +4472,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">_xlfn.MODE.MULT({4,4,4})</f>
@@ -4451,10 +4487,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">SUM(_xlfn.MODE.MULT({1,1,2,2,3,3}))</f>
@@ -4466,10 +4502,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">_xlfn.MODE.MULT({5,5,6,7})</f>
@@ -4481,10 +4517,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="C8" s="7" t="b">
         <f t="array" ref="C8">ISNUMBER(SUM(_xlfn.MODE.MULT({1,1,2,2,3})))</f>
@@ -4496,10 +4532,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C9" s="10" t="str">
         <f t="array" ref="C9">_xlfn.MODE.MULT({1,2,3})</f>
@@ -4514,7 +4550,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">_xlfn.MODE.MULT()</f>
@@ -4558,10 +4594,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C2" s="4">
         <f>_xlfn.MODE.SNGL(1,2,2,3)</f>
@@ -4576,7 +4612,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">_xlfn.MODE.SNGL({1,1,2,3,3,3})</f>
@@ -4588,10 +4624,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C4" s="4">
         <f>_xlfn.MODE.SNGL(5,5,5)</f>
@@ -4603,10 +4639,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C5" s="4">
         <f>_xlfn.MODE.SNGL(1,1,2,2)</f>
@@ -4618,10 +4654,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C6" s="4">
         <f>_xlfn.MODE.SNGL(1,2,3,2,1,2,3,2)</f>
@@ -4633,10 +4669,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="C7" s="4">
         <f>_xlfn.MODE.SNGL(7,7)</f>
@@ -4648,10 +4684,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="C8" s="7">
         <f>_xlfn.MODE.SNGL(1,2,2,3)-MODE(1,2,2,3)</f>
@@ -4663,10 +4699,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C9" s="10" t="str">
         <f>_xlfn.MODE.SNGL(1,2,3)</f>
@@ -4681,7 +4717,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>_xlfn.MODE.SNGL()</f>
@@ -4907,10 +4943,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">PERCENTILE({1,2,3,4,5},0.5)</f>
@@ -4922,10 +4958,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">PERCENTILE({1,2,3,4,5},0)</f>
@@ -4937,10 +4973,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">PERCENTILE({1,2,3,4,5},1)</f>
@@ -4952,10 +4988,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">PERCENTILE({1,2,3,4,5},0.25)</f>
@@ -4967,10 +5003,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">PERCENTILE({1,2,3,4,5},0.75)</f>
@@ -4982,10 +5018,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">PERCENTILE(5,0.5)</f>
@@ -4997,10 +5033,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="C8" s="4">
         <f t="array" ref="C8">PERCENTILE({1,3},0.5)</f>
@@ -5012,10 +5048,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">ROUND(PERCENTILE({1,2,3,4,5},0.333),4)</f>
@@ -5027,10 +5063,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">PERCENTILE({1,2,3},1.1)</f>
@@ -5045,7 +5081,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>PERCENTILE()</f>
@@ -5089,10 +5125,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">_xlfn.PERCENTILE.EXC({1,2,3,4,5},0.5)</f>
@@ -5104,10 +5140,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">_xlfn.PERCENTILE.EXC({1,2,3,4,5},0.25)</f>
@@ -5119,10 +5155,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">_xlfn.PERCENTILE.EXC({1,2,3,4,5},0.75)</f>
@@ -5134,10 +5170,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">_xlfn.PERCENTILE.EXC({1,2,3,4,5},0.1667)</f>
@@ -5149,10 +5185,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">_xlfn.PERCENTILE.EXC({1,2,3,4,5},0.8333)</f>
@@ -5164,10 +5200,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="C7" s="7">
         <f t="array" ref="C7">ROUND(_xlfn.PERCENTILE.EXC({1,2,3,4,5},0.25),4)</f>
@@ -5179,10 +5215,10 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C8" s="10" t="str">
         <f t="array" ref="C8">_xlfn.PERCENTILE.EXC({1,2,3},0)</f>
@@ -5194,10 +5230,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="C9" s="10" t="str">
         <f t="array" ref="C9">_xlfn.PERCENTILE.EXC({1,2,3},1)</f>
@@ -5209,10 +5245,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">_xlfn.PERCENTILE.EXC({1,2,3},1.5)</f>
@@ -5227,7 +5263,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>_xlfn.PERCENTILE.EXC()</f>
@@ -5271,10 +5307,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">_xlfn.PERCENTILE.INC({1,2,3,4,5},0.5)</f>
@@ -5286,10 +5322,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">_xlfn.PERCENTILE.INC({1,2,3,4,5},0)</f>
@@ -5301,10 +5337,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">_xlfn.PERCENTILE.INC({1,2,3,4,5},1)</f>
@@ -5316,10 +5352,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">_xlfn.PERCENTILE.INC({1,2,3,4,5},0.25)</f>
@@ -5331,10 +5367,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">_xlfn.PERCENTILE.INC({1,2,3,4,5},0.75)</f>
@@ -5346,10 +5382,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">_xlfn.PERCENTILE.INC({1,3},0.5)</f>
@@ -5361,10 +5397,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C8" s="4">
         <f t="array" ref="C8">_xlfn.PERCENTILE.INC(5,0)</f>
@@ -5376,10 +5412,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">_xlfn.PERCENTILE.INC({1,2,3,4,5},0.5)-PERCENTILE({1,2,3,4,5},0.5)</f>
@@ -5391,10 +5427,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">_xlfn.PERCENTILE.INC({1,2,3},1.1)</f>
@@ -5409,7 +5445,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>_xlfn.PERCENTILE.INC()</f>
@@ -5453,10 +5489,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">PERCENTRANK({1,2,3,4,5},3)</f>
@@ -5468,10 +5504,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">PERCENTRANK({1,2,3,4,5},1)</f>
@@ -5483,10 +5519,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">PERCENTRANK({1,2,3,4,5},5)</f>
@@ -5498,10 +5534,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">ROUND(PERCENTRANK({1,2,3,4,5},2),2)</f>
@@ -5513,10 +5549,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">ROUND(PERCENTRANK({1,2,2,3},2),4)</f>
@@ -5528,10 +5564,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">PERCENTRANK({1,2,3},1)</f>
@@ -5543,10 +5579,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="C8" s="7">
         <f t="array" ref="C8">ROUND(PERCENTRANK({1,2,3,4,5},3),4)</f>
@@ -5558,10 +5594,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C9" s="10" t="str">
         <f t="array" ref="C9">PERCENTRANK({1,2,3},0)</f>
@@ -5573,10 +5609,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">PERCENTRANK({1,2,3},4)</f>
@@ -5591,7 +5627,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>PERCENTRANK()</f>
@@ -5635,10 +5671,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">ROUND(_xlfn.PERCENTRANK.EXC({1,2,3,4,5},3),4)</f>
@@ -5650,10 +5686,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">ROUND(_xlfn.PERCENTRANK.EXC({1,2,3,4,5},1),4)</f>
@@ -5665,10 +5701,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">ROUND(_xlfn.PERCENTRANK.EXC({1,2,3,4,5},5),4)</f>
@@ -5680,10 +5716,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">ROUND(_xlfn.PERCENTRANK.EXC({1,2,3,4,5},2),4)</f>
@@ -5695,10 +5731,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">ROUND(_xlfn.PERCENTRANK.EXC({1,2,3},2),4)</f>
@@ -5710,10 +5746,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">ROUND(_xlfn.PERCENTRANK.EXC({1,2,2,3},2),4)</f>
@@ -5725,10 +5761,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C8" s="7" t="b">
         <f t="array" ref="C8">_xlfn.PERCENTRANK.EXC({1,2,3,4,5},1)&lt;&gt;PERCENTRANK({1,2,3,4,5},1)</f>
@@ -5740,10 +5776,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="C9" s="10" t="str">
         <f t="array" ref="C9">_xlfn.PERCENTRANK.EXC({1,2,3},4)</f>
@@ -5755,10 +5791,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">_xlfn.PERCENTRANK.EXC({1,2,3},0)</f>
@@ -5773,7 +5809,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>_xlfn.PERCENTRANK.EXC()</f>
@@ -5817,10 +5853,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">_xlfn.PERCENTRANK.INC({1,2,3,4,5},3)</f>
@@ -5832,10 +5868,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">_xlfn.PERCENTRANK.INC({1,2,3,4,5},1)</f>
@@ -5847,10 +5883,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">_xlfn.PERCENTRANK.INC({1,2,3,4,5},5)</f>
@@ -5862,10 +5898,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">ROUND(_xlfn.PERCENTRANK.INC({1,2,3,4,5},2),4)</f>
@@ -5877,10 +5913,10 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="C6" s="7">
         <f t="array" ref="C6">_xlfn.PERCENTRANK.INC({1,2,3,4,5},3)-PERCENTRANK({1,2,3,4,5},3)</f>
@@ -5892,10 +5928,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">ROUND(_xlfn.PERCENTRANK.INC({1,2,2,3},2),4)</f>
@@ -5907,10 +5943,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="C8" s="4">
         <f t="array" ref="C8">_xlfn.PERCENTRANK.INC({1,2,3},1)</f>
@@ -5922,10 +5958,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="C9" s="7" t="b">
         <f t="array" ref="C9">ISNUMBER(_xlfn.PERCENTRANK.INC({1,2,3,4,5},3))</f>
@@ -5937,10 +5973,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">_xlfn.PERCENTRANK.INC({1,2,3},0)</f>
@@ -5955,7 +5991,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>_xlfn.PERCENTRANK.INC()</f>
@@ -5999,10 +6035,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">QUARTILE({1,2,3,4,5},1)</f>
@@ -6014,10 +6050,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">QUARTILE({1,2,3,4,5},2)</f>
@@ -6029,10 +6065,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">QUARTILE({1,2,3,4,5},3)</f>
@@ -6044,10 +6080,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">QUARTILE({1,2,3,4,5},0)</f>
@@ -6059,10 +6095,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">QUARTILE({1,2,3,4,5},4)</f>
@@ -6074,10 +6110,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">QUARTILE(5,0)</f>
@@ -6089,10 +6125,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="C8" s="4">
         <f t="array" ref="C8">QUARTILE({1,3},2)</f>
@@ -6104,10 +6140,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">QUARTILE({1,2,3,4,5},2)-MEDIAN({1,2,3,4,5})</f>
@@ -6119,10 +6155,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">QUARTILE({1,2,3},5)</f>
@@ -6137,7 +6173,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>QUARTILE()</f>
@@ -6181,10 +6217,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">_xlfn.QUARTILE.EXC({1,2,3,4,5},1)</f>
@@ -6196,10 +6232,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">_xlfn.QUARTILE.EXC({1,2,3,4,5},2)</f>
@@ -6211,10 +6247,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">_xlfn.QUARTILE.EXC({1,2,3,4,5},3)</f>
@@ -6226,10 +6262,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">ROUND(_xlfn.QUARTILE.EXC({1,2,3,4,5,6,7,8},1),4)</f>
@@ -6241,10 +6277,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">ROUND(_xlfn.QUARTILE.EXC({1,2,3,4,5,6,7,8},3),4)</f>
@@ -6256,10 +6292,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C7" s="7">
         <f t="array" ref="C7">_xlfn.QUARTILE.EXC({1,2,3,4,5},2)-MEDIAN({1,2,3,4,5})</f>
@@ -6271,10 +6307,10 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C8" s="10" t="str">
         <f t="array" ref="C8">_xlfn.QUARTILE.EXC({1,2,3},0)</f>
@@ -6286,10 +6322,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="C9" s="10" t="str">
         <f t="array" ref="C9">_xlfn.QUARTILE.EXC({1,2,3},4)</f>
@@ -6304,7 +6340,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>_xlfn.QUARTILE.EXC()</f>
@@ -6348,10 +6384,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">_xlfn.QUARTILE.INC({1,2,3,4,5},1)</f>
@@ -6363,10 +6399,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">_xlfn.QUARTILE.INC({1,2,3,4,5},2)</f>
@@ -6378,10 +6414,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">_xlfn.QUARTILE.INC({1,2,3,4,5},3)</f>
@@ -6393,10 +6429,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">_xlfn.QUARTILE.INC({1,2,3,4,5},0)</f>
@@ -6408,10 +6444,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">_xlfn.QUARTILE.INC({1,2,3,4,5},4)</f>
@@ -6423,10 +6459,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C7" s="7">
         <f t="array" ref="C7">_xlfn.QUARTILE.INC({1,2,3,4,5},1)-QUARTILE({1,2,3,4,5},1)</f>
@@ -6438,10 +6474,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="C8" s="4">
         <f t="array" ref="C8">_xlfn.QUARTILE.INC({1,3},2)</f>
@@ -6453,10 +6489,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">_xlfn.QUARTILE.INC({1,2,3,4,5},2)-MEDIAN({1,2,3,4,5})</f>
@@ -6468,10 +6504,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">_xlfn.QUARTILE.INC({1,2,3},5)</f>
@@ -6486,7 +6522,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>_xlfn.QUARTILE.INC()</f>
@@ -6530,10 +6566,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">RANK(3,{1,2,3,4,5})</f>
@@ -6545,10 +6581,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">RANK(5,{1,2,3,4,5})</f>
@@ -6560,10 +6596,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">RANK(1,{1,2,3,4,5},1)</f>
@@ -6575,10 +6611,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">RANK(3,{1,2,3,4,5},1)</f>
@@ -6590,10 +6626,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">RANK(3,{1,3,3,5})</f>
@@ -6605,10 +6641,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">RANK(1,{1,2,3,4,5})</f>
@@ -6620,10 +6656,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C8" s="4">
         <f t="array" ref="C8">RANK(5,{3,5})</f>
@@ -6635,10 +6671,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">RANK(3,{1,2,3,4,5})+RANK(3,{1,2,3,4,5},1)</f>
@@ -6650,10 +6686,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">RANK(6,{1,2,3,4,5})</f>
@@ -6668,7 +6704,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>RANK()</f>
@@ -6690,10 +6726,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.5"/>
-    <col customWidth="1" min="2" max="2" width="38.63"/>
+    <col customWidth="1" min="1" max="1" width="33.88"/>
+    <col customWidth="1" min="2" max="2" width="42.75"/>
     <col customWidth="1" min="3" max="3" width="14.13"/>
-    <col customWidth="1" min="4" max="4" width="5.88"/>
+    <col customWidth="1" min="4" max="4" width="7.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6801,33 +6837,33 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="10" t="str">
-        <f t="array" ref="C8">AVERAGEIF({1,2,3},"&gt;"&amp;10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>27</v>
+      <c r="C8" s="4">
+        <f t="array" ref="C8">AVERAGEIF({10,20,30},20)</f>
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="7">
-        <f t="array" ref="C9">ROUND(AVERAGEIF({1,2,3,4,5},"&gt;"&amp;2),4)</f>
-        <v>4</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>24</v>
+      <c r="C9" s="4">
+        <f t="array" ref="C9">AVERAGEIF({1,2,3},"&lt;&gt;"&amp;2)</f>
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -6837,26 +6873,116 @@
       <c r="B10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="4">
-        <f t="array" ref="C10">AVERAGEIF({10,20,30},20)</f>
-        <v>20</v>
+      <c r="C10" s="4" t="str">
+        <f t="array" ref="C10">AVERAGEIF({"ab","ac","ba"},"a?",{10,20,30})</f>
+        <v>#N/A</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="4" t="str">
+        <f t="array" ref="C11">AVERAGEIF({"Apple","APPLE","banana"},"apple",{10,20,30})</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="4">
+        <f t="array" ref="C12">AVERAGEIF({1,2,3,4,5},"&gt;="&amp;3)</f>
+        <v>4</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="13" t="str">
+        <f t="array" ref="C13">AVERAGEIF({1,2,3},"2",{10,20,30})</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="10" t="str">
+        <f t="array" ref="C14">AVERAGEIF({1,2,3},"&gt;"&amp;10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="7">
+        <f t="array" ref="C15">ROUND(AVERAGEIF({1,2,3,4,5},"&gt;"&amp;2),4)</f>
+        <v>4</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="7">
+        <f t="array" ref="C16">ROUND(AVERAGEIF({1,2,3},"&gt;"&amp;0)-AVERAGE({1,2,3}),10)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="10" t="str">
+      <c r="B17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="10" t="str">
         <f>AVERAGEIF()</f>
         <v>#N/A</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6894,10 +7020,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">_xlfn.RANK.AVG(3,{1,2,3,4,5})</f>
@@ -6909,10 +7035,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">_xlfn.RANK.AVG(3,{1,2,3,3,5})</f>
@@ -6924,10 +7050,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">_xlfn.RANK.AVG(1,{1,2,3})</f>
@@ -6939,10 +7065,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">_xlfn.RANK.AVG(5,{1,2,3,4,5})</f>
@@ -6954,10 +7080,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">_xlfn.RANK.AVG(2,{1,2,2,2,5})</f>
@@ -6969,10 +7095,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">_xlfn.RANK.AVG(2,{1,2,2,3},1)</f>
@@ -6984,10 +7110,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C8" s="4">
         <f t="array" ref="C8">_xlfn.RANK.AVG(3,{3,5})</f>
@@ -6999,10 +7125,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">_xlfn.RANK.AVG(3,{1,2,3,4,5})-RANK(3,{1,2,3,4,5})</f>
@@ -7014,10 +7140,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">_xlfn.RANK.AVG(6,{1,2,3})</f>
@@ -7032,7 +7158,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>_xlfn.RANK.AVG()</f>
@@ -7076,10 +7202,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">_xlfn.RANK.EQ(3,{1,2,3,4,5})</f>
@@ -7091,10 +7217,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">_xlfn.RANK.EQ(3,{1,2,3,3,5})</f>
@@ -7106,10 +7232,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">_xlfn.RANK.EQ(5,{1,2,3,4,5})</f>
@@ -7121,10 +7247,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">_xlfn.RANK.EQ(1,{1,2,3,4,5},1)</f>
@@ -7136,10 +7262,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">_xlfn.RANK.EQ(2,{1,2,2,2,5})</f>
@@ -7151,10 +7277,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">_xlfn.RANK.EQ(1,{1,2,3,4,5})</f>
@@ -7166,10 +7292,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C8" s="4">
         <f t="array" ref="C8">_xlfn.RANK.EQ(5,{3,5})</f>
@@ -7181,10 +7307,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">_xlfn.RANK.EQ(3,{1,2,3,4,5})-RANK(3,{1,2,3,4,5})</f>
@@ -7196,10 +7322,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">_xlfn.RANK.EQ(6,{1,2,3})</f>
@@ -7214,7 +7340,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>_xlfn.RANK.EQ()</f>
@@ -7258,10 +7384,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="C2" s="4">
         <f>ROUND(SKEW(3,4,5,2,3,4,5,6,4,7),4)</f>
@@ -7273,10 +7399,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C3" s="4">
         <f>ROUND(SKEW(1,2,3,4,5,4,3,2,1),4)</f>
@@ -7291,7 +7417,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="C4" s="4" t="str">
         <f>SKEW(1,1,1,1)</f>
@@ -7303,10 +7429,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="C5" s="4">
         <f>ROUND(SKEW(1,2,3,3,3,4,4,10),4)</f>
@@ -7318,10 +7444,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C6" s="4">
         <f>ROUND(SKEW(1,1,1,2,3,4,5,6),4)</f>
@@ -7333,10 +7459,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C7" s="4">
         <f>ROUND(SKEW(1,2,3,4,10),4)</f>
@@ -7348,10 +7474,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="C8" s="7" t="b">
         <f>ISNUMBER(SKEW(1,2,3,4,5))</f>
@@ -7363,10 +7489,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="C9" s="10" t="str">
         <f>SKEW(1,2)</f>
@@ -7381,7 +7507,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>SKEW()</f>
@@ -7425,10 +7551,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C2" s="4">
         <f>ROUND(_xlfn.SKEW.P(1,2,3,4,5),6)</f>
@@ -7443,7 +7569,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C3" s="4" t="str">
         <f>_xlfn.SKEW.P(3,3,3,3)</f>
@@ -7455,10 +7581,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="C4" s="4">
         <f>ROUND(_xlfn.SKEW.P(1,1,1,2,3,4,10),4)</f>
@@ -7470,10 +7596,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C5" s="4">
         <f>ROUND(_xlfn.SKEW.P(1,2,3,4,9),4)</f>
@@ -7485,10 +7611,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="C6" s="4" t="b">
         <f>ISNUMBER(_xlfn.SKEW.P(1,2,3,4,5))</f>
@@ -7500,10 +7626,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="C7" s="4">
         <f>ROUND(_xlfn.SKEW.P(1,2,3,4,5,6),6)</f>
@@ -7515,10 +7641,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="C8" s="7">
         <f>ROUND(_xlfn.SKEW.P(1,2,3,4,5),4)</f>
@@ -7530,10 +7656,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="C9" s="10" t="str">
         <f>_xlfn.SKEW.P(1,2)</f>
@@ -7548,7 +7674,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>_xlfn.SKEW.P()</f>
@@ -7592,10 +7718,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">SMALL({3,1,4,1,5,9,2,6},1)</f>
@@ -7607,10 +7733,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">SMALL({3,1,4,1,5,9,2,6},2)</f>
@@ -7622,10 +7748,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">SMALL({3,1,4,1,5,9,2,6},3)</f>
@@ -7637,10 +7763,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">SMALL({1,2,3},3)</f>
@@ -7652,10 +7778,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">SMALL({5,5,5},1)</f>
@@ -7667,10 +7793,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">SMALL(42,1)</f>
@@ -7682,10 +7808,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="C8" s="4">
         <f t="array" ref="C8">SMALL({7,3},1)</f>
@@ -7697,10 +7823,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">LARGE({1,2,3,4,5},1)+SMALL({1,2,3,4,5},1)</f>
@@ -7712,10 +7838,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">SMALL({1,2,3},0)</f>
@@ -7727,10 +7853,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C11" s="10" t="str">
         <f t="array" ref="C11">SMALL({1,2,3},4)</f>
@@ -7745,7 +7871,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="C12" s="10" t="str">
         <f>SMALL()</f>
@@ -7789,10 +7915,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="C2" s="4">
         <f>ROUND(STDEV(2,4,4,4,5,5,7,9),4)</f>
@@ -7804,10 +7930,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">ROUND(STDEV({1,2,3,4,5}),6)</f>
@@ -7822,7 +7948,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="C4" s="4">
         <f>STDEV(5,5,5)</f>
@@ -7837,7 +7963,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="C5" s="4">
         <f>STDEV(1,3)</f>
@@ -7852,7 +7978,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="C6" s="4">
         <f>ROUND(STDEV(-1,0,1),6)</f>
@@ -7867,7 +7993,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C7" s="4">
         <f>ROUND(STDEV(0,100),4)</f>
@@ -7879,10 +8005,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="C8" s="7">
         <f t="array" ref="C8">ROUND(STDEV({1,2,3,4,5})-_xlfn.STDEV.S({1,2,3,4,5}),10)</f>
@@ -7894,10 +8020,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="C9" s="7">
         <f>ROUND(STDEV(1,2,3,4,5),4)</f>
@@ -7909,10 +8035,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>STDEV(5)</f>
@@ -7927,7 +8053,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>STDEV()</f>
@@ -7971,10 +8097,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="C2" s="4">
         <f>ROUND(_xlfn.STDEV.P(2,4,4,4,5,5,7,9),4)</f>
@@ -7986,10 +8112,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">ROUND(_xlfn.STDEV.P({1,2,3,4,5}),6)</f>
@@ -8004,7 +8130,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="C4" s="4">
         <f>_xlfn.STDEV.P(5,5,5)</f>
@@ -8019,7 +8145,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="C5" s="4">
         <f>_xlfn.STDEV.P(5)</f>
@@ -8034,7 +8160,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="C6" s="4">
         <f>_xlfn.STDEV.P(1,3)</f>
@@ -8049,7 +8175,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="C7" s="4">
         <f>ROUND(_xlfn.STDEV.P(-1,0,1),6)</f>
@@ -8061,10 +8187,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="C8" s="7">
         <f t="array" ref="C8">ROUND(_xlfn.STDEV.P({1,2,3,4,5})-STDEVP({1,2,3,4,5}),10)</f>
@@ -8076,10 +8202,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="C9" s="7">
         <f>ROUND(_xlfn.STDEV.P(1,2,3,4,5),4)</f>
@@ -8094,7 +8220,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>_xlfn.STDEV.P()</f>
@@ -8138,10 +8264,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">ROUND(_xlfn.STDEV.S({1,2,3,4,5}),6)</f>
@@ -8153,10 +8279,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="C3" s="4">
         <f>ROUND(_xlfn.STDEV.S(2,4,4,4,5,5,7,9),4)</f>
@@ -8171,7 +8297,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="C4" s="4">
         <f>_xlfn.STDEV.S(5,5,5)</f>
@@ -8186,7 +8312,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="C5" s="4">
         <f>_xlfn.STDEV.S(1,3)</f>
@@ -8201,7 +8327,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="C6" s="4">
         <f>ROUND(_xlfn.STDEV.S(-1,0,1),6)</f>
@@ -8213,10 +8339,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="C7" s="7">
         <f t="array" ref="C7">ROUND(_xlfn.STDEV.S({1,2,3,4,5})-STDEV({1,2,3,4,5}),10)</f>
@@ -8228,10 +8354,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="C8" s="7">
         <f>ROUND(_xlfn.STDEV.S(1,2,3,4,5),4)</f>
@@ -8243,10 +8369,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="C9" s="10" t="str">
         <f>_xlfn.STDEV.S(5)</f>
@@ -8261,7 +8387,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>_xlfn.STDEV.S()</f>
@@ -8305,10 +8431,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="C2" s="4">
         <f>ROUND(STDEVA(1,2,3,4,5),4)</f>
@@ -8320,10 +8446,10 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C3" s="13">
         <f>ROUND(STDEVA(TRUE,FALSE,1),6)</f>
@@ -8335,10 +8461,10 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="C4" s="13" t="str">
         <f>ROUND(STDEVA("text",1,2),6)</f>
@@ -8353,7 +8479,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="C5" s="4">
         <f>STDEVA(5,5,5)</f>
@@ -8368,7 +8494,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="C6" s="4">
         <f>STDEVA(1,3)</f>
@@ -8383,7 +8509,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="C7" s="4">
         <f>ROUND(STDEVA(-1,0,1),6)</f>
@@ -8395,10 +8521,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="C8" s="7">
         <f>ROUND(STDEVA(1,2,3,4,5)-STDEV(1,2,3,4,5),10)</f>
@@ -8410,10 +8536,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="C9" s="7">
         <f>ROUND(STDEVA(1,2,3,4,5),4)</f>
@@ -8425,10 +8551,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>STDEVA(5)</f>
@@ -8443,7 +8569,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>STDEVA()</f>
@@ -8487,10 +8613,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">ROUND(STDEVP({1,2,3,4,5}),6)</f>
@@ -8502,10 +8628,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="C3" s="4">
         <f>ROUND(STDEVP(2,4,4,4,5,5,7,9),4)</f>
@@ -8520,7 +8646,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="C4" s="4">
         <f>STDEVP(5,5,5)</f>
@@ -8535,7 +8661,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="C5" s="4">
         <f>STDEVP(5)</f>
@@ -8547,10 +8673,10 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="C6" s="7">
         <f t="array" ref="C6">ROUND(STDEVP({1,2,3,4,5})-_xlfn.STDEV.P({1,2,3,4,5}),10)</f>
@@ -8565,7 +8691,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="C7" s="4">
         <f>STDEVP(1,3)</f>
@@ -8580,7 +8706,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="C8" s="4">
         <f>ROUND(STDEVP(-1,0,1),6)</f>
@@ -8592,10 +8718,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="C9" s="7">
         <f>ROUND(STDEVP(1,2,3,4,5),4)</f>
@@ -8610,7 +8736,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>STDEVP()</f>
@@ -8654,10 +8780,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C2" s="4" t="str">
         <f t="array" ref="C2">AVERAGEIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;"&amp;2)</f>
@@ -8669,10 +8795,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C3" s="4" t="str">
         <f t="array" ref="C3">AVERAGEIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;"&amp;1,{1,2,3,4,5},"&lt;"&amp;5)</f>
@@ -8684,10 +8810,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C4" s="4" t="str">
         <f t="array" ref="C4">AVERAGEIFS({10,20,30},{"a","b","a"},"a")</f>
@@ -8699,10 +8825,10 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C5" s="10" t="str">
         <f t="array" ref="C5">AVERAGEIFS({1,2,3},{1,2,3},"&gt;"&amp;100)</f>
@@ -8714,10 +8840,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C6" s="4" t="str">
         <f t="array" ref="C6">AVERAGEIFS({1,2,3},{1,2,3},2)</f>
@@ -8729,10 +8855,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C7" s="4" t="str">
         <f t="array" ref="C7">AVERAGEIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;="&amp;3)</f>
@@ -8744,10 +8870,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C8" s="7" t="str">
         <f t="array" ref="C8">ROUND(AVERAGEIFS({1,2,3,4,5},{1,2,3,4,5},"&gt;"&amp;1,{1,2,3,4,5},"&lt;"&amp;5),4)</f>
@@ -8759,10 +8885,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C9" s="4" t="str">
         <f t="array" ref="C9">AVERAGEIFS(42,1,1)</f>
@@ -8777,7 +8903,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>AVERAGEIFS()</f>
@@ -8821,10 +8947,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">ROUND(STDEVPA({1,2,3,4,5}),6)</f>
@@ -8836,10 +8962,10 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="C3" s="13">
         <f>ROUND(STDEVPA(TRUE,FALSE,1),6)</f>
@@ -8851,10 +8977,10 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="C4" s="13" t="str">
         <f>ROUND(STDEVPA("text",1,2),6)</f>
@@ -8869,7 +8995,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="C5" s="4">
         <f>STDEVPA(5,5,5)</f>
@@ -8884,7 +9010,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="C6" s="4">
         <f>STDEVPA(5)</f>
@@ -8896,10 +9022,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C7" s="7">
         <f>ROUND(STDEVPA(1,2,3,4,5)-_xlfn.STDEV.P(1,2,3,4,5),10)</f>
@@ -8914,7 +9040,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="C8" s="4">
         <f>STDEVPA(1,3)</f>
@@ -8926,10 +9052,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="C9" s="7">
         <f>ROUND(STDEVPA(1,2,3,4,5),4)</f>
@@ -8944,7 +9070,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>STDEVPA()</f>
@@ -8988,10 +9114,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">TRIMMEAN({1,2,3,4,5,6,7,8,9,10},0.2)</f>
@@ -9003,10 +9129,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">TRIMMEAN({1,2,3,4,5},0)</f>
@@ -9018,10 +9144,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">TRIMMEAN({1,2,3,4,5,6,7,8,9,10},0.1)</f>
@@ -9033,10 +9159,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">TRIMMEAN({1,2,3,4,5,6,7,8,9,10},0.4)</f>
@@ -9048,10 +9174,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">TRIMMEAN({1,2,3,4,5,5,4,3,2,1},0.2)</f>
@@ -9063,10 +9189,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">TRIMMEAN({1,2,3},0.99)</f>
@@ -9078,10 +9204,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="C8" s="4">
         <f t="array" ref="C8">ROUND(TRIMMEAN({2,2,2,2,2},0.2),10)</f>
@@ -9093,10 +9219,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">ROUND(TRIMMEAN({1,2,3,4,5,6,7,8,9,10},0.2),4)</f>
@@ -9108,10 +9234,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">TRIMMEAN({1,2,3},-0.1)</f>
@@ -9126,7 +9252,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>TRIMMEAN()</f>
@@ -9170,10 +9296,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="C2" s="4">
         <f>VAR(2,4,4,4,5,5,7,9)</f>
@@ -9185,10 +9311,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">VAR({1,2,3,4,5})</f>
@@ -9203,7 +9329,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="C4" s="4">
         <f>VAR(5,5,5)</f>
@@ -9218,7 +9344,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="C5" s="4">
         <f>VAR(1,3)</f>
@@ -9233,7 +9359,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="C6" s="4">
         <f>VAR(-1,0,1)</f>
@@ -9248,7 +9374,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="C7" s="4">
         <f>VAR(0,100)</f>
@@ -9260,10 +9386,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="C8" s="7">
         <f t="array" ref="C8">VAR({1,2,3,4,5})-_xlfn.VAR.S({1,2,3,4,5})</f>
@@ -9275,10 +9401,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">ROUND(VAR({1,2,3,4,5}),4)</f>
@@ -9290,10 +9416,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>VAR(5)</f>
@@ -9308,7 +9434,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>VAR()</f>
@@ -9352,10 +9478,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="C2" s="4">
         <f>_xlfn.VAR.P(2,4,4,4,5,5,7,9)</f>
@@ -9367,10 +9493,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">_xlfn.VAR.P({1,2,3,4,5})</f>
@@ -9385,7 +9511,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="C4" s="4">
         <f>_xlfn.VAR.P(5,5,5)</f>
@@ -9400,7 +9526,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="C5" s="4">
         <f>_xlfn.VAR.P(5)</f>
@@ -9415,7 +9541,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="C6" s="4">
         <f>_xlfn.VAR.P(1,3)</f>
@@ -9430,7 +9556,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="C7" s="4">
         <f>_xlfn.VAR.P(-1,0,1)</f>
@@ -9442,10 +9568,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="C8" s="7">
         <f t="array" ref="C8">_xlfn.VAR.P({1,2,3,4,5})-VARP({1,2,3,4,5})</f>
@@ -9457,10 +9583,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">ROUND(_xlfn.VAR.P({1,2,3,4,5}),4)</f>
@@ -9475,7 +9601,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>_xlfn.VAR.P()</f>
@@ -9519,10 +9645,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">_xlfn.VAR.S({1,2,3,4,5})</f>
@@ -9534,10 +9660,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="C3" s="4">
         <f>_xlfn.VAR.S(2,4,4,4,5,5,7,9)</f>
@@ -9552,7 +9678,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="C4" s="4">
         <f>_xlfn.VAR.S(5,5,5)</f>
@@ -9567,7 +9693,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="C5" s="4">
         <f>_xlfn.VAR.S(1,3)</f>
@@ -9582,7 +9708,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="C6" s="4">
         <f>_xlfn.VAR.S(-1,0,1)</f>
@@ -9594,10 +9720,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="C7" s="7">
         <f t="array" ref="C7">_xlfn.VAR.S({1,2,3,4,5})-VAR({1,2,3,4,5})</f>
@@ -9609,10 +9735,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="C8" s="7">
         <f t="array" ref="C8">ROUND(_xlfn.VAR.S({1,2,3,4,5}),4)</f>
@@ -9624,10 +9750,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="C9" s="10" t="str">
         <f>_xlfn.VAR.S(5)</f>
@@ -9642,7 +9768,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>_xlfn.VAR.S()</f>
@@ -9686,10 +9812,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="C2" s="4">
         <f>VARA(1,2,3,4,5)</f>
@@ -9701,10 +9827,10 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="C3" s="13">
         <f>ROUND(VARA(TRUE,FALSE,1),6)</f>
@@ -9716,10 +9842,10 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="C4" s="13" t="str">
         <f>ROUND(VARA("text",1,2),6)</f>
@@ -9734,7 +9860,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="C5" s="4">
         <f>VARA(5,5,5)</f>
@@ -9749,7 +9875,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="C6" s="4">
         <f>VARA(1,3)</f>
@@ -9764,7 +9890,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="C7" s="4">
         <f>VARA(-1,0,1)</f>
@@ -9776,10 +9902,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="C8" s="7">
         <f>VARA(1,2,3,4,5)-VAR(1,2,3,4,5)</f>
@@ -9791,10 +9917,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="C9" s="7">
         <f>ROUND(VARA(1,2,3,4,5),4)</f>
@@ -9806,10 +9932,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>VARA(5)</f>
@@ -9824,7 +9950,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>VARA()</f>
@@ -9868,10 +9994,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">VARP({1,2,3,4,5})</f>
@@ -9883,10 +10009,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="C3" s="4">
         <f>VARP(2,4,4,4,5,5,7,9)</f>
@@ -9901,7 +10027,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="C4" s="4">
         <f>VARP(5,5,5)</f>
@@ -9916,7 +10042,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="C5" s="4">
         <f>VARP(5)</f>
@@ -9928,10 +10054,10 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="C6" s="7">
         <f t="array" ref="C6">VARP({1,2,3,4,5})-_xlfn.VAR.P({1,2,3,4,5})</f>
@@ -9946,7 +10072,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="C7" s="4">
         <f>VARP(1,3)</f>
@@ -9961,7 +10087,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="C8" s="4">
         <f>VARP(-1,0,1)</f>
@@ -9973,10 +10099,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">ROUND(VARP({1,2,3,4,5}),4)</f>
@@ -9991,7 +10117,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>VARP()</f>
@@ -10035,10 +10161,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">VARPA({1,2,3,4,5})</f>
@@ -10050,10 +10176,10 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="C3" s="13">
         <f>ROUND(VARPA(TRUE,FALSE,1),6)</f>
@@ -10065,10 +10191,10 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="C4" s="13" t="str">
         <f>ROUND(VARPA("text",1,2),6)</f>
@@ -10083,7 +10209,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="C5" s="4">
         <f>VARPA(5,5,5)</f>
@@ -10098,7 +10224,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="C6" s="4">
         <f>VARPA(5)</f>
@@ -10110,10 +10236,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="C7" s="7">
         <f>VARPA(1,2,3,4,5)-VARP(1,2,3,4,5)</f>
@@ -10128,7 +10254,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="C8" s="4">
         <f>VARPA(1,3)</f>
@@ -10140,10 +10266,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="C9" s="7">
         <f>ROUND(VARPA(1,2,3,4,5),4)</f>
@@ -10158,7 +10284,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>VARPA()</f>
@@ -10202,10 +10328,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">ROUND(_xlfn.COVARIANCE.P({2,4,4,4,5,5,7,9},{4,2,3,4,5,6,6,7}),4)</f>
@@ -10217,10 +10343,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">ROUND(_xlfn.COVARIANCE.P({1,2,3},{1,2,3}),6)</f>
@@ -10232,10 +10358,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">_xlfn.COVARIANCE.P({1,2},{2,1})</f>
@@ -10247,10 +10373,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">_xlfn.COVARIANCE.P({1,2,3},{3,3,3})</f>
@@ -10262,10 +10388,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">_xlfn.COVARIANCE.P({1,3},{1,3})</f>
@@ -10277,10 +10403,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">ROUND(_xlfn.COVARIANCE.P({100,200,300},{1,2,3}),4)</f>
@@ -10292,10 +10418,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C8" s="7">
         <f t="array" ref="C8">ROUND(_xlfn.COVARIANCE.P({1,2,3,4,5},{5,4,3,2,1}),6)</f>
@@ -10307,10 +10433,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C9" s="4">
         <f t="array" ref="C9">_xlfn.COVARIANCE.P(5,5)</f>
@@ -10322,10 +10448,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C10" s="10" t="str">
         <f t="array" ref="C10">_xlfn.COVARIANCE.P(1,{2,3})</f>
@@ -10340,7 +10466,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>_xlfn.COVARIANCE.P()</f>
@@ -10384,10 +10510,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">ROUND(_xlfn.COVARIANCE.S({1,2,3},{1,2,3}),6)</f>
@@ -10399,10 +10525,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C3" s="4">
         <f t="array" ref="C3">_xlfn.COVARIANCE.S({1,2},{2,1})</f>
@@ -10414,10 +10540,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">ROUND(_xlfn.COVARIANCE.S({1,2,3},{3,4,5}),6)</f>
@@ -10429,10 +10555,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C5" s="4">
         <f t="array" ref="C5">ROUND(_xlfn.COVARIANCE.S({1,2,3,4,5},{5,4,3,2,1}),6)</f>
@@ -10444,10 +10570,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C6" s="4">
         <f t="array" ref="C6">_xlfn.COVARIANCE.S({1,2,3},{3,3,3})</f>
@@ -10462,7 +10588,7 @@
         <v>20</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C7" s="4">
         <f t="array" ref="C7">ROUND(_xlfn.COVARIANCE.S({0,100},{100,0}),4)</f>
@@ -10474,10 +10600,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C8" s="7">
         <f t="array" ref="C8">ROUND(_xlfn.COVARIANCE.S({1,2,3},{1,2,3})-_xlfn.VAR.S({1,2,3}),10)</f>
@@ -10489,10 +10615,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C9" s="10" t="str">
         <f t="array" ref="C9">_xlfn.COVARIANCE.S(1,1)</f>
@@ -10507,7 +10633,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>_xlfn.COVARIANCE.S()</f>
@@ -10551,10 +10677,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C2" s="4">
         <f t="array" ref="C2">DEVSQ({1,2,3,4,5})</f>
@@ -10566,10 +10692,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C3" s="4">
         <f>DEVSQ(2,4,4,4,5,5,7,9)</f>
@@ -10584,7 +10710,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C4" s="4">
         <f>DEVSQ(5,5,5)</f>
@@ -10599,7 +10725,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C5" s="4">
         <f>DEVSQ(1,3)</f>
@@ -10614,7 +10740,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C6" s="4">
         <f>DEVSQ(5)</f>
@@ -10629,7 +10755,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C7" s="4">
         <f>DEVSQ(-1,0,1)</f>
@@ -10644,7 +10770,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C8" s="4">
         <f>ROUND(DEVSQ(1.5,2.5,3.5),10)</f>
@@ -10656,10 +10782,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C9" s="7">
         <f t="array" ref="C9">ROUND(DEVSQ({1,2,3,4,5})/(5-1)-_xlfn.VAR.S({1,2,3,4,5}),10)</f>
@@ -10671,10 +10797,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C10" s="4">
         <f>DEVSQ(100,200,300)</f>
@@ -10689,7 +10815,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>DEVSQ()</f>
@@ -10733,10 +10859,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C2" s="4">
         <f>GEOMEAN(1,4)</f>
@@ -10748,10 +10874,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C3" s="4">
         <f>ROUND(GEOMEAN(1,2,4,8),6)</f>
@@ -10766,7 +10892,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">GEOMEAN({4,9})</f>
@@ -10778,10 +10904,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C5" s="4">
         <f>GEOMEAN(16)</f>
@@ -10793,10 +10919,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C6" s="4">
         <f>GEOMEAN(1,1,1)</f>
@@ -10808,10 +10934,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C7" s="4">
         <f>ROUND(GEOMEAN(10,1000),4)</f>
@@ -10823,10 +10949,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C8" s="7">
         <f>ROUND(GEOMEAN(10,40),4)</f>
@@ -10838,10 +10964,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C9" s="10" t="str">
         <f>GEOMEAN(-1,4)</f>
@@ -10853,10 +10979,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>GEOMEAN(0,4)</f>
@@ -10871,7 +10997,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>GEOMEAN()</f>
@@ -10918,7 +11044,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C2" s="4">
         <f>ROUND(HARMEAN(1,2),6)</f>
@@ -10930,10 +11056,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C3" s="4">
         <f>ROUND(HARMEAN(1,2,4),6)</f>
@@ -10948,7 +11074,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C4" s="4">
         <f t="array" ref="C4">HARMEAN({40,60})</f>
@@ -10960,10 +11086,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C5" s="4">
         <f>HARMEAN(5,5,5)</f>
@@ -10975,10 +11101,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C6" s="4">
         <f>HARMEAN(10)</f>
@@ -10990,10 +11116,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C7" s="4">
         <f>ROUND(HARMEAN(100,200,400),4)</f>
@@ -11005,10 +11131,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C8" s="7">
         <f>ROUND(HARMEAN(1,2,4),4)</f>
@@ -11020,10 +11146,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C9" s="10" t="str">
         <f>HARMEAN(0,1)</f>
@@ -11035,10 +11161,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C10" s="10" t="str">
         <f>HARMEAN(-1,1)</f>
@@ -11053,7 +11179,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C11" s="10" t="str">
         <f>HARMEAN()</f>
